--- a/demo_data/sectors/uretim_sanayi/ar_aging.xlsx
+++ b/demo_data/sectors/uretim_sanayi/ar_aging.xlsx
@@ -474,7 +474,7 @@
         <v>46000</v>
       </c>
       <c r="D2" t="n">
-        <v>276383.56</v>
+        <v>259515.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         <v>45997</v>
       </c>
       <c r="D3" t="n">
-        <v>276383.56</v>
+        <v>259515.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         <v>46020</v>
       </c>
       <c r="D4" t="n">
-        <v>276383.56</v>
+        <v>259515.08</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         <v>46064</v>
       </c>
       <c r="D5" t="n">
-        <v>362753.42</v>
+        <v>340613.54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         <v>46064</v>
       </c>
       <c r="D6" t="n">
-        <v>362753.42</v>
+        <v>340613.55</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>46030</v>
       </c>
       <c r="D7" t="n">
-        <v>621863.01</v>
+        <v>583908.9300000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         <v>46058</v>
       </c>
       <c r="D8" t="n">
-        <v>621863.01</v>
+        <v>583908.9300000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>46039</v>
       </c>
       <c r="D9" t="n">
-        <v>172739.73</v>
+        <v>162196.93</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>46024</v>
       </c>
       <c r="D10" t="n">
-        <v>172739.73</v>
+        <v>162196.93</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>46040</v>
       </c>
       <c r="D11" t="n">
-        <v>172739.73</v>
+        <v>162196.92</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>45983</v>
       </c>
       <c r="D12" t="n">
-        <v>259109.59</v>
+        <v>243295.39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45982</v>
       </c>
       <c r="D13" t="n">
-        <v>259109.59</v>
+        <v>243295.39</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>46083</v>
       </c>
       <c r="D14" t="n">
-        <v>518219.18</v>
+        <v>486590.78</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>46018</v>
       </c>
       <c r="D15" t="n">
-        <v>414575.34</v>
+        <v>389272.62</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>46017</v>
       </c>
       <c r="D16" t="n">
-        <v>138191.78</v>
+        <v>129757.54</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>46034</v>
       </c>
       <c r="D17" t="n">
-        <v>138191.78</v>
+        <v>129757.54</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46023</v>
       </c>
       <c r="D18" t="n">
-        <v>138191.78</v>
+        <v>129757.54</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46047</v>
       </c>
       <c r="D19" t="n">
-        <v>138191.78</v>
+        <v>129757.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>46049</v>
       </c>
       <c r="D20" t="n">
-        <v>138191.78</v>
+        <v>129757.54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46044</v>
       </c>
       <c r="D21" t="n">
-        <v>138191.78</v>
+        <v>129757.54</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45999</v>
       </c>
       <c r="D22" t="n">
-        <v>207287.67</v>
+        <v>194636.31</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46006</v>
       </c>
       <c r="D23" t="n">
-        <v>207287.67</v>
+        <v>194636.31</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46055</v>
       </c>
       <c r="D24" t="n">
-        <v>120917.81</v>
+        <v>113537.85</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46072</v>
       </c>
       <c r="D25" t="n">
-        <v>120917.81</v>
+        <v>113537.85</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>46047</v>
       </c>
       <c r="D26" t="n">
-        <v>120917.81</v>
+        <v>113537.84</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>45989</v>
       </c>
       <c r="D27" t="n">
-        <v>362753.42</v>
+        <v>340613.54</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>46007</v>
       </c>
       <c r="D28" t="n">
-        <v>155465.75</v>
+        <v>145977.23</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>46005</v>
       </c>
       <c r="D29" t="n">
-        <v>155465.75</v>
+        <v>145977.24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46093</v>
       </c>
       <c r="D30" t="n">
-        <v>310931.51</v>
+        <v>291954.47</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46027</v>
       </c>
       <c r="D31" t="n">
-        <v>155465.75</v>
+        <v>145977.23</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>46026</v>
       </c>
       <c r="D32" t="n">
-        <v>155465.75</v>
+        <v>145977.24</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>46105</v>
       </c>
       <c r="D33" t="n">
-        <v>129554.79</v>
+        <v>121647.7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46113</v>
       </c>
       <c r="D34" t="n">
-        <v>129554.79</v>
+        <v>121647.69</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46026</v>
       </c>
       <c r="D35" t="n">
-        <v>129554.79</v>
+        <v>121647.7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>46015</v>
       </c>
       <c r="D36" t="n">
-        <v>129554.79</v>
+        <v>121647.69</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>46065</v>
       </c>
       <c r="D37" t="n">
-        <v>259109.59</v>
+        <v>243295.39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>46139</v>
       </c>
       <c r="D38" t="n">
-        <v>129554.79</v>
+        <v>121647.7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46125</v>
       </c>
       <c r="D39" t="n">
-        <v>129554.79</v>
+        <v>121647.69</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46004</v>
       </c>
       <c r="D40" t="n">
-        <v>103643.84</v>
+        <v>97318.14999999999</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46019</v>
       </c>
       <c r="D41" t="n">
-        <v>103643.84</v>
+        <v>97318.16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>46157</v>
       </c>
       <c r="D42" t="n">
-        <v>103643.84</v>
+        <v>97318.14999999999</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46156</v>
       </c>
       <c r="D43" t="n">
-        <v>103643.84</v>
+        <v>97318.16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46070</v>
       </c>
       <c r="D44" t="n">
-        <v>103643.84</v>
+        <v>97318.14999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>46058</v>
       </c>
       <c r="D45" t="n">
-        <v>103643.84</v>
+        <v>97318.16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46099</v>
       </c>
       <c r="D46" t="n">
-        <v>69095.89</v>
+        <v>64878.77</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>46098</v>
       </c>
       <c r="D47" t="n">
-        <v>69095.89</v>
+        <v>64878.77</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>46118</v>
       </c>
       <c r="D48" t="n">
-        <v>69095.89</v>
+        <v>64878.77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>46031</v>
       </c>
       <c r="D49" t="n">
-        <v>207287.67</v>
+        <v>194636.31</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>46034</v>
       </c>
       <c r="D50" t="n">
-        <v>77732.88</v>
+        <v>72988.62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>46039</v>
       </c>
       <c r="D51" t="n">
-        <v>77732.88</v>
+        <v>72988.61</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>46084</v>
       </c>
       <c r="D52" t="n">
-        <v>155465.75</v>
+        <v>145977.23</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46041</v>
       </c>
       <c r="D53" t="n">
-        <v>77732.88</v>
+        <v>72988.62</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>46047</v>
       </c>
       <c r="D54" t="n">
-        <v>77732.88</v>
+        <v>72988.61</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45992</v>
       </c>
       <c r="D55" t="n">
-        <v>77732.88</v>
+        <v>72988.62</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45998</v>
       </c>
       <c r="D56" t="n">
-        <v>77732.88</v>
+        <v>72988.61</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46023</v>
       </c>
       <c r="D57" t="n">
-        <v>77732.88</v>
+        <v>72988.62</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46038</v>
       </c>
       <c r="D58" t="n">
-        <v>77732.88</v>
+        <v>72988.61</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>46064</v>
       </c>
       <c r="D59" t="n">
-        <v>51821.92</v>
+        <v>48659.08</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46063</v>
       </c>
       <c r="D60" t="n">
-        <v>51821.92</v>
+        <v>48659.08</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>46059</v>
       </c>
       <c r="D61" t="n">
-        <v>34547.95</v>
+        <v>32439.39</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>46076</v>
       </c>
       <c r="D62" t="n">
-        <v>34547.95</v>
+        <v>32439.39</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>46077</v>
       </c>
       <c r="D63" t="n">
-        <v>34547.95</v>
+        <v>32439.38</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>46099</v>
       </c>
       <c r="D64" t="n">
-        <v>103643.84</v>
+        <v>97318.16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>46007</v>
       </c>
       <c r="D65" t="n">
-        <v>34547.95</v>
+        <v>32439.39</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>46005</v>
       </c>
       <c r="D66" t="n">
-        <v>34547.95</v>
+        <v>32439.39</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>46014</v>
       </c>
       <c r="D67" t="n">
-        <v>34547.95</v>
+        <v>32439.38</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46028</v>
       </c>
       <c r="D68" t="n">
-        <v>51821.92</v>
+        <v>48659.08</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>46040</v>
       </c>
       <c r="D69" t="n">
-        <v>51821.92</v>
+        <v>48659.08</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>

--- a/demo_data/sectors/uretim_sanayi/ar_aging.xlsx
+++ b/demo_data/sectors/uretim_sanayi/ar_aging.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="D2" t="n">
-        <v>259515.08</v>
+        <v>383866.06</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="D3" t="n">
-        <v>259515.08</v>
+        <v>383866.06</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46020</v>
+        <v>46007</v>
       </c>
       <c r="D4" t="n">
-        <v>259515.08</v>
+        <v>383866.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="D5" t="n">
-        <v>340613.54</v>
+        <v>1036438.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kalyon Altyapı Yatırımları A.Ş.</t>
+          <t>Şişecam Düzcam Pazarlama A.Ş.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46064</v>
+        <v>46012</v>
       </c>
       <c r="D6" t="n">
-        <v>340613.55</v>
+        <v>921278.54</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Şişecam Düzcam Pazarlama A.Ş.</t>
+          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46030</v>
+        <v>46041</v>
       </c>
       <c r="D7" t="n">
-        <v>583908.9300000001</v>
+        <v>268706.24</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eczacıbaşı Yapı Gereçleri A.Ş.</t>
+          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46058</v>
+        <v>46026</v>
       </c>
       <c r="D8" t="n">
-        <v>583908.9300000001</v>
+        <v>268706.24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46039</v>
+        <v>46042</v>
       </c>
       <c r="D9" t="n">
-        <v>162196.93</v>
+        <v>268706.24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
+          <t>Arçelik Pazarlama A.Ş.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46024</v>
+        <v>45985</v>
       </c>
       <c r="D10" t="n">
-        <v>162196.93</v>
+        <v>403059.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestel Beyaz Eşya Sanayi A.Ş.</t>
+          <t>Arçelik Pazarlama A.Ş.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46040</v>
+        <v>45984</v>
       </c>
       <c r="D11" t="n">
-        <v>162196.92</v>
+        <v>403059.36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Arçelik Pazarlama A.Ş.</t>
+          <t>Ford Otosan Tedarik Sanayi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45983</v>
+        <v>46085</v>
       </c>
       <c r="D12" t="n">
-        <v>243295.39</v>
+        <v>806118.72</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Arçelik Pazarlama A.Ş.</t>
+          <t>Tofaş Türk Otomobil Fabrikası</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45982</v>
+        <v>46020</v>
       </c>
       <c r="D13" t="n">
-        <v>243295.39</v>
+        <v>690958.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ford Otosan Tedarik Sanayi</t>
+          <t>Aselsan Elektronik Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46083</v>
+        <v>46124</v>
       </c>
       <c r="D14" t="n">
-        <v>486590.78</v>
+        <v>230319.63</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tofaş Türk Otomobil Fabrikası</t>
+          <t>Aselsan Elektronik Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46018</v>
+        <v>46141</v>
       </c>
       <c r="D15" t="n">
-        <v>389272.62</v>
+        <v>230319.63</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BİM Birleşik Mağazalar A.Ş.</t>
+          <t>Aselsan Elektronik Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46017</v>
+        <v>46130</v>
       </c>
       <c r="D16" t="n">
-        <v>129757.54</v>
+        <v>230319.64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BİM Birleşik Mağazalar A.Ş.</t>
+          <t>Havelsan Hava Elektronik Sanayi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46034</v>
+        <v>46024</v>
       </c>
       <c r="D17" t="n">
-        <v>129757.54</v>
+        <v>191933.03</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BİM Birleşik Mağazalar A.Ş.</t>
+          <t>Havelsan Hava Elektronik Sanayi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46023</v>
+        <v>46021</v>
       </c>
       <c r="D18" t="n">
-        <v>129757.54</v>
+        <v>191933.03</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Migros Ticaret Dağıtım A.Ş.</t>
+          <t>Havelsan Hava Elektronik Sanayi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46047</v>
+        <v>46017</v>
       </c>
       <c r="D19" t="n">
-        <v>129757.54</v>
+        <v>191933.03</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Migros Ticaret Dağıtım A.Ş.</t>
+          <t>Tekfen İmalat ve Montaj A.Ş.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46049</v>
+        <v>46153</v>
       </c>
       <c r="D20" t="n">
-        <v>129757.54</v>
+        <v>575799.09</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Migros Ticaret Dağıtım A.Ş.</t>
+          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46044</v>
+        <v>46017</v>
       </c>
       <c r="D21" t="n">
-        <v>129757.54</v>
+        <v>191933.03</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Anadolu Efes Dağıtım A.Ş.</t>
+          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="D22" t="n">
-        <v>194636.31</v>
+        <v>191933.03</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Anadolu Efes Dağıtım A.Ş.</t>
+          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="D23" t="n">
-        <v>194636.31</v>
+        <v>191933.03</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ülker Bisküvi Sanayi A.Ş.</t>
+          <t>Kardemir Karabük Demir Çelik</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46055</v>
+        <v>46047</v>
       </c>
       <c r="D24" t="n">
-        <v>113537.85</v>
+        <v>153546.42</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ülker Bisküvi Sanayi A.Ş.</t>
+          <t>Kardemir Karabük Demir Çelik</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46072</v>
+        <v>46044</v>
       </c>
       <c r="D25" t="n">
-        <v>113537.85</v>
+        <v>153546.42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ülker Bisküvi Sanayi A.Ş.</t>
+          <t>Kardemir Karabük Demir Çelik</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46047</v>
+        <v>46042</v>
       </c>
       <c r="D26" t="n">
-        <v>113537.84</v>
+        <v>153546.43</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Trendyol Pazaryeri Satış A.Ş.</t>
+          <t>Petkim Petrokimya Holding A.Ş.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="D27" t="n">
-        <v>340613.54</v>
+        <v>460639.27</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hepsiburada E-Ticaret A.Ş.</t>
+          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="D28" t="n">
-        <v>145977.23</v>
+        <v>230319.64</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hepsiburada E-Ticaret A.Ş.</t>
+          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46005</v>
+        <v>46021</v>
       </c>
       <c r="D29" t="n">
-        <v>145977.24</v>
+        <v>230319.63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LC Waikiki Mağazacılık A.Ş.</t>
+          <t>Ereğli Makine İmalat Ltd.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46093</v>
+        <v>46047</v>
       </c>
       <c r="D30" t="n">
-        <v>291954.47</v>
+        <v>172739.73</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DeFacto Perakende Ticaret A.Ş.</t>
+          <t>Ereğli Makine İmalat Ltd.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1138,886 +1138,12 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="D31" t="n">
-        <v>145977.23</v>
+        <v>172739.72</v>
       </c>
       <c r="E31" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>DeFacto Perakende Ticaret A.Ş.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FA-1031</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>46026</v>
-      </c>
-      <c r="D32" t="n">
-        <v>145977.24</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>FA-1032</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="D33" t="n">
-        <v>121647.7</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Turkcell İletişim Hizmetleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FA-1033</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="D34" t="n">
-        <v>121647.69</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Vodafone Telekomünikasyon A.Ş.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FA-1034</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>46026</v>
-      </c>
-      <c r="D35" t="n">
-        <v>121647.7</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Vodafone Telekomünikasyon A.Ş.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>FA-1035</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>46015</v>
-      </c>
-      <c r="D36" t="n">
-        <v>121647.69</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Türk Telekomünikasyon A.Ş.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>FA-1036</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="D37" t="n">
-        <v>243295.39</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Aselsan Elektronik Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FA-1037</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>46139</v>
-      </c>
-      <c r="D38" t="n">
-        <v>121647.7</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Aselsan Elektronik Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FA-1038</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>46125</v>
-      </c>
-      <c r="D39" t="n">
-        <v>121647.69</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Havelsan Hava Elektronik Sanayi</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FA-1039</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>46004</v>
-      </c>
-      <c r="D40" t="n">
-        <v>97318.14999999999</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Havelsan Hava Elektronik Sanayi</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>FA-1040</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>46019</v>
-      </c>
-      <c r="D41" t="n">
-        <v>97318.16</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Tekfen İnşaat ve Tesisat A.Ş.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FA-1041</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D42" t="n">
-        <v>97318.14999999999</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Tekfen İnşaat ve Tesisat A.Ş.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FA-1042</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D43" t="n">
-        <v>97318.16</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Limak İnşaat Sanayi ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FA-1043</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>46070</v>
-      </c>
-      <c r="D44" t="n">
-        <v>97318.14999999999</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Limak İnşaat Sanayi ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FA-1044</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="D45" t="n">
-        <v>97318.16</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cengiz İnşaat Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FA-1045</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="D46" t="n">
-        <v>64878.77</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cengiz İnşaat Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>FA-1046</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="D47" t="n">
-        <v>64878.77</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Cengiz İnşaat Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>FA-1047</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="D48" t="n">
-        <v>64878.77</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>İÇDAŞ Çelik Enerji Tersane A.Ş.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>FA-1048</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="D49" t="n">
-        <v>194636.31</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Kardemir Karabük Demir Çelik</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>FA-1049</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="D50" t="n">
-        <v>72988.62</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Kardemir Karabük Demir Çelik</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>FA-1050</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>46039</v>
-      </c>
-      <c r="D51" t="n">
-        <v>72988.61</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Akçansa Çimento Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>FA-1051</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>46084</v>
-      </c>
-      <c r="D52" t="n">
-        <v>145977.23</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Çimsa Çimento Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>FA-1052</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>46041</v>
-      </c>
-      <c r="D53" t="n">
-        <v>72988.62</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Çimsa Çimento Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FA-1053</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>46047</v>
-      </c>
-      <c r="D54" t="n">
-        <v>72988.61</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Petkim Petrokimya Holding A.Ş.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>FA-1054</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="D55" t="n">
-        <v>72988.62</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Petkim Petrokimya Holding A.Ş.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FA-1055</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>45998</v>
-      </c>
-      <c r="D56" t="n">
-        <v>72988.61</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FA-1056</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="D57" t="n">
-        <v>72988.62</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Tüpraş Türkiye Petrol Rafinerileri</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>FA-1057</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>46038</v>
-      </c>
-      <c r="D58" t="n">
-        <v>72988.61</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Doğuş Otomotiv Servis ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>FA-1058</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>46064</v>
-      </c>
-      <c r="D59" t="n">
-        <v>48659.08</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Doğuş Otomotiv Servis ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>FA-1059</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>46063</v>
-      </c>
-      <c r="D60" t="n">
-        <v>48659.08</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Koçtaş Yapı Marketleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>FA-1060</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="D61" t="n">
-        <v>32439.39</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Koçtaş Yapı Marketleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>FA-1061</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>46076</v>
-      </c>
-      <c r="D62" t="n">
-        <v>32439.39</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Koçtaş Yapı Marketleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>FA-1062</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>46077</v>
-      </c>
-      <c r="D63" t="n">
-        <v>32439.38</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Teknosa İç ve Dış Ticaret A.Ş.</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>FA-1063</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="D64" t="n">
-        <v>97318.16</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>CarrefourSA Hipermarketleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>FA-1064</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>46007</v>
-      </c>
-      <c r="D65" t="n">
-        <v>32439.39</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>CarrefourSA Hipermarketleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>FA-1065</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>46005</v>
-      </c>
-      <c r="D66" t="n">
-        <v>32439.39</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>CarrefourSA Hipermarketleri A.Ş.</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>FA-1066</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>46014</v>
-      </c>
-      <c r="D67" t="n">
-        <v>32439.38</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Şok Marketler Ticaret A.Ş.</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>FA-1067</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>46028</v>
-      </c>
-      <c r="D68" t="n">
-        <v>48659.08</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Şok Marketler Ticaret A.Ş.</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>FA-1068</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="D69" t="n">
-        <v>48659.08</v>
-      </c>
-      <c r="E69" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
